--- a/GL/upload/UploadInvItems/Copy of PRC_Service_List.xlsx
+++ b/GL/upload/UploadInvItems/Copy of PRC_Service_List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wajah\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B06BFE6-B8B7-40EE-AC5A-BA1EAB60AC9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB7387FE-3CEB-48B3-911E-B314A559DF51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
